--- a/artfynd/A 8236-2025 artfynd.xlsx
+++ b/artfynd/A 8236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127834542</v>
       </c>
       <c r="B2" t="n">
-        <v>58144</v>
+        <v>58147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127834667</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127834540</v>
       </c>
       <c r="B4" t="n">
-        <v>58306</v>
+        <v>58309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8236-2025 artfynd.xlsx
+++ b/artfynd/A 8236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127834542</v>
       </c>
       <c r="B2" t="n">
-        <v>58147</v>
+        <v>58153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127834667</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127834540</v>
       </c>
       <c r="B4" t="n">
-        <v>58309</v>
+        <v>58315</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8236-2025 artfynd.xlsx
+++ b/artfynd/A 8236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127834542</v>
       </c>
       <c r="B2" t="n">
-        <v>58153</v>
+        <v>58154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127834667</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127834540</v>
       </c>
       <c r="B4" t="n">
-        <v>58315</v>
+        <v>58316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8236-2025 artfynd.xlsx
+++ b/artfynd/A 8236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127834542</v>
       </c>
       <c r="B2" t="n">
-        <v>58154</v>
+        <v>58166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>127834667</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127834540</v>
       </c>
       <c r="B4" t="n">
-        <v>58316</v>
+        <v>58328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
